--- a/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_10092026.xlsx
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-1.06</v>
+        <v>-1.02</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-1.28</v>
+        <v>-1.25</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-1.5</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="7">
@@ -2747,19 +2747,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3.87</v>
+        <v>3.97</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="9">
@@ -2791,19 +2791,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>7.14</v>
+        <v>7.28</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>5.24</v>
+        <v>5.35</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="10">
@@ -2813,19 +2813,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>7.34</v>
+        <v>7.47</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>6.62</v>
+        <v>6.74</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="11"/>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>The 10% ad-valorem duty back, charged on every export tonne for ever (5.0966), or at half that rate (6.5857)</t>
+          <t>The 10% ad-valorem duty back, charged on every export tonne for ever (6.0079), or at half that rate (7.6216)</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>5.096633765309656</v>
+        <v>6.007894010425169</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2903,11 +2903,11 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Priced at the retired typed US$280/t, the weakest-sourced input in a 304-input register, whose source string was four words long and named no assessor, series, date or basis (7.5002)</t>
+          <t>Priced at the retired typed US$280/t, the weakest-sourced input in a 304-input register, whose source string was four words long and named no assessor, series, date or basis (8.5859)</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>7.500162299446612</v>
+        <v>8.585904517238273</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>5.407252661808486</v>
+        <v>6.049238568022454</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>5.264107281415742</v>
+        <v>5.848175733657654</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>6.027419537013731</v>
+        <v>6.762386572972461</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>9.293905460682925</v>
+        <v>10.72755798678344</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>5.072710422990149</v>
+        <v>5.988876947264754</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>8.806789404390324</v>
+        <v>10.06273572951017</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>7.082167477332161</v>
+        <v>8.237225793240649</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>5.457073757897384</v>
+        <v>6.276678789271338</v>
       </c>
       <c r="D27" s="11">
         <f>C27-$D$15</f>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>9.009779646164183</v>
+        <v>10.24650026555612</v>
       </c>
       <c r="D28" s="11">
         <f>C28-$D$15</f>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>7.870008717622996</v>
+        <v>9.032017599293999</v>
       </c>
       <c r="D29" s="11">
         <f>C29-$D$15</f>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>11.60654207035342</v>
+        <v>12.77234373196298</v>
       </c>
     </row>
     <row r="37">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>9.092881689457943</v>
+        <v>9.61514893727578</v>
       </c>
     </row>
     <row r="39">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>8.074785424029702</v>
+        <v>9.235379308069334</v>
       </c>
     </row>
     <row r="24">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>11.60654207035342</v>
+        <v>12.77234373196298</v>
       </c>
     </row>
     <row r="25">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="C117" s="15" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
